--- a/data_extactor/batch_10_fa/batch_0094_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0094_fa.xlsx
@@ -508,27 +508,27 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | مانیتورینگ | سخن گفتن | یادگیری فعال | گوش دادن فعال | درک مطلب خواندن</t>
+          <t>تفکر انتقادی | نظارت | سخن گفتن | یادگیری فعال | گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | مکانیک | زبان انگلیسی | تولید مواد غذایی | مدیریت و سازماندهی | ریاضیات | ایمنی و امنیت عمومی | آموزش و پرورش</t>
+          <t>تولید و فرآوری | مکانیک | زبان انگلیسی | تولید مواد غذایی | مدیریت و اداره | ریاضیات | ایمنی و امنیت عمومی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | حساسیت به مشکل | استدلال قیاسی | سرعت ادراکی | ثبات بازو-دست | قدرت تنه | قدرت ایستا | زمان عکس‌العمل | دقت کنترل | چالاکی انگشتان | چالاکی دست | بیان شفاهی | وضوح گفتار | تشخیص گفتار | کنترل نرخ | هماهنگی چند عضو | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال استقرایی | بیان کتبی | درک کتبی | درک شفاهی</t>
+          <t>بینایی نزدیک | حساسیت به مسئله | استدلال قیاسی | سرعت ادراکی | ثبات دست و بازو | قدرت تنه | قدرت ایستا | زمان عکس‌العمل | دقت کنترل | مهارت انگشتان | مهارت دستی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | کنترل نرخ | هماهنگی چند عضو | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال استقرایی | بیان کتبی | درک کتبی | درک شفاهی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | بحث‌های چهره به چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض صداها و سطوح نویز مزاحم یا ناراحت‌کننده | داخل ساختمان، با محیط کنترل‌شده | صرف زمان به صورت ایستاده | سلامت و ایمنی سایر کارگران | اهمیت دقیق یا بی‌نقص بودن | فشار زمانی | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | تاثیر تصمیمات بر همکاران یا نتایج شرکت | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | فراوانی تصمیم‌گیری | سرعت تعیین‌شده توسط سرعت تجهیزات | ارتباط با دیگران | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | اهمیت تکرار وظایف یکسان | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | پیامدهای کاری و نتایج سایر کارگران | نامه‌ها و یادداشت‌های کتبی | قرار گرفتن در معرض تجهیزات خطرناک | قرار گرفتن در معرض آلاینده‌ها | استفاده از تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، هارنس ایمنی، لباس‌های محافظ کامل یا حفاظت در برابر تشعشع | داخل ساختمان، بدون محیط کنترل‌شده</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای ایستادن | سلامت و ایمنی سایر کارکنان | اهمیت دقیق یا درست بودن | فشار زمانی | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | تأثیر تصمیمات بر همکاران یا نتایج شرکت | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | فراوانی تصمیم‌گیری | سرعت تعیین‌شده توسط سرعت تجهیزات | ارتباط با دیگران | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | اهمیت تکرار وظایف یکسان | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | پیامدهای کاری و نتایج سایر کارکنان | نامه‌ها و یادداشت‌های کتبی | قرار گرفتن در معرض تجهیزات خطرناک | قرار گرفتن در معرض آلاینده‌ها | استفاده از تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، هارنس ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع | محیط داخلی، بدون کنترل شرایط محیطی</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>تکنسین‌های نیروگاه زیست‌توده | اپراتورها و متصدیان تجهیزات تمیزکاری، شستشو و اسیدشویی فلزات | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های سنگ‌شکن، آسیاب و پولیش | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکسترود و فرم‌دهی الیاف مصنوعی و شیشه | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکسترود، فرم‌دهی، پرس و متراکم‌سازی | دست‌اندرکاران بچینگ مواد غذایی | اپراتورها و متصدیان دستگاه‌های پخت مواد غذایی | اپراتورها و متصدیان دستگاه‌های برشته‌کاری، پخت و خشک‌کردن مواد غذایی و تنباکو | اپراتورها و متصدیان کوره، کوره پخت، فر، خشک‌کن و دیگ بخار | اپراتورهای کمپرسور گاز و ایستگاه پمپاژ گاز | تنظیم‌کنندگان، اپراتورها و متصدیان تجهیزات عملیات حرارتی فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | اپراتورها و متصدیان کوره‌های تصفیه فلز | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های مخلوط‌کن و ترکیب‌کننده | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک | اپراتورها و متصدیان دستگاه‌های بسته‌بندی و پرکن | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های تولید محصولات کاغذی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های نورد فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های جداسازی، فیلتراسیون، شفاف‌سازی، رسوب‌دهی و تقطیر | مهندسان تاسیسات و اپراتورهای دیگ بخار</t>
+          <t>تکنسین‌های نیروگاه زیست‌توده | اپراتورها و متصدیان تجهیزات تمیزکاری، شستشو و اسیدشویی فلزات | تنظیم‌کاران، اپراتورها و متصدیان ماشین‌آلات خردایش، آسیاب و پرداخت | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن، شکل‌دهی، پرس و متراکم‌سازی | بچ‌سازان مواد غذایی | اپراتورها و متصدیان ماشین‌های پخت مواد غذایی | اپراتورها و متصدیان ماشین‌های برشته‌کاری، پخت و خشک‌کردن مواد غذایی و تنباکو | اپراتورها و متصدیان کوره، کوره پخت، فر، خشک‌کن و دیگ بخار | اپراتورهای کمپرسور گاز و ایستگاه پمپاژ گاز | تنظیم‌کنندگان، اپراتورها و متصدیان تجهیزات عملیات حرارتی، فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | اپراتورها و متصدیان کوره تصفیه فلز | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های مخلوط‌کن و ترکیب‌کننده | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاست | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های تولید محصولات کاغذی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های نورد، فلز و پلاستیک | تنظیم‌کاران، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، زلال‌سازی، ته‌نشینی و تقطیر | مهندسان تاسیسات و اپراتورهای دیگ بخار</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,27 +565,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب خواندن | مانیتورینگ | تفکر انتقادی | سخن گفتن | گوش دادن فعال</t>
+          <t>درک مطلب | نظارت | تفکر انتقادی | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | خدمات مشتریان و پرسنل | مکانیک | طراحی</t>
+          <t>تولید و فرآوری | خدمات مشتری و شخصی | مکانیک | طراحی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | ثبات بازو-دست | دقت کنترل | درک شفاهی | بیان شفاهی | توجه انتخابی | چالاکی دست | چالاکی انگشتان | وضوح گفتار | تشخیص گفتار | تجسم فضایی | حساسیت به مشکل | درک کتبی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال استقرایی | استدلال قیاسی | روان بودن ایده‌ها</t>
+          <t>بینایی نزدیک | ثبات دست و بازو | دقت کنترل | درک شفاهی | بیان شفاهی | توجه انتخابی | مهارت دستی | مهارت انگشتان | وضوح گفتار | تشخیص گفتار | تجسم | حساسیت به مسئله | درک کتبی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال استقرایی | استدلال قیاسی | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>بحث‌های چهره به چهره با افراد و درون تیم‌ها | اهمیت دقیق یا بی‌نقص بودن | داخل ساختمان، با محیط کنترل‌شده | صرف زمان برای استفاده از دست‌ها جهت جابجایی, کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فشار زمانی | قرار گرفتن در معرض آلاینده‌ها | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | مکالمات تلفنی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض صداها و سطوح نویز مزاحم یا ناراحت‌کننده</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فشار زمانی | قرار گرفتن در معرض آلاینده‌ها | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | مکالمات تلفنی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های پوشش‌دهی، رنگ‌آمیزی و اسپری | برش‌کاران و آرایش‌دهندگان دستی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و اسلایس | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش، پانچ و پرس فلز و پلاستیک | الگوسازان پارچه و پوشاک | کارگران سنگ‌زنی و پولیش دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای سنگ‌زنی، لپینگ، پولیش و پرداخت فلز و پلاستیک | جواهرسازان و کارگران سنگ‌ها و فلزات قیمتی | کارگران چیدمان و علامت‌گذاری فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های فرز و صفحه تراش فلز و پلاستیک | مدل‌سازان فلز و پلاستیک | قالب‌سازان، شکل‌دهندگان و ریخته‌گران به جز فلز و پلاستیک | تکنسین‌های آزمایشگاه چشم‌پزشکی | کارگران رنگ‌آمیزی، پوشش‌دهی و تزیین | الگوسازان فلز و پلاستیک | تکنسین‌ها و کارگران پیش از چاپ | اپراتورهای ماشین چاپ | سنگ‌تراشان و قلم‌زنان سنگ، تولیدی | تیزکنندگان و فیلرکنندگان ابزار و سنگ‌ساب‌ها | قالب‌سازان و ابزارسازان</t>
+          <t>تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های پوشش‌دهی، نقاشی و اسپری | برش‌دهندگان و پرداخت‌کاران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش، پانچ و پرس، فلز و پلاستیک | الگوسازان پارچه و پوشاک | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و صیقل‌کاری فلز و پلاستیک | جواهرسازان و کارگران سنگ‌ها و فلزات قیمتی | کارگران شابلون‌زنی، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات فرزکاری و صفحه‌تراشی فلز و پلاستیک | مدل‌سازان فلز و پلاستیک | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | تکنسین‌های آزمایشگاه چشم‌پزشکی | کارگران نقاشی، پوشش‌دهی و تزیین | الگوسازان فلز و پلاستیک | تکنسین‌ها و کارگران پیش از چاپ | اپراتورهای ماشین چاپ | سنگ‌تراشان و قلم‌زنان سنگ، تولیدی | سنگ‌زنان، سوهان‌کاران و تیزکنندگان ابزار | سازندگان ابزار و قالب</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>مانیتورینگ | گوش دادن فعال | تفکر انتقادی | درک مطلب خواندن | سخن گفتن | ریاضیات</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن | ریاضیات</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -632,17 +632,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>ثبات بازو-دست | چالاکی انگشتان | چالاکی دست | دقت کنترل | بینایی نزدیک | هماهنگی چند عضو | توجه انتخابی | درک شفاهی | انعطاف‌پذیری بدنی | ترتیب‌دهی اطلاعات | استدلال استقرایی | استدلال قیاسی</t>
+          <t>ثبات دست و بازو | مهارت انگشتان | مهارت دستی | دقت کنترل | بینایی نزدیک | هماهنگی چند عضو | توجه انتخابی | درک شفاهی | انعطاف‌پذیری دامنه حرکت | ترتیب‌دهی اطلاعات | استدلال استقرایی | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان به صورت ایستاده | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض صداها و سطوح نویز مزاحم یا ناراحت‌کننده | اهمیت دقیق یا بی‌نقص بودن | فشار زمانی | کار با یا مشارکت در یک گروه کاری یا تیم | داخل ساختمان، بدون محیط کنترل‌شده | ارتباط با دیگران | صرف زمان برای راه رفتن یا دویدن | بحث‌های چهره به چهره با افراد و درون تیم‌ها | سرعت تعیین‌شده توسط سرعت تجهیزات | قرار گرفتن در معرض آلاینده‌ها | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | صرف زمان برای خم شدن یا پیچاندن بدن | قرار گرفتن در معرض سوختگی‌های جزئی، برش‌ها، گازگرفتگی‌ها یا نیش‌ها</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای ایستادن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | اهمیت دقیق یا درست بودن | فشار زمانی | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، بدون کنترل شرایط محیطی | ارتباط با دیگران | صرف زمان برای راه رفتن یا دویدن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | سرعت تعیین‌شده توسط سرعت تجهیزات | قرار گرفتن در معرض آلاینده‌ها | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | صرف زمان برای خم کردن یا چرخاندن بدن | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان دستگاه‌های اتصال چسبی | برش‌کاران و آرایش‌دهندگان دستی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و اسلایس | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکسترود، فرم‌دهی، پرس و متراکم‌سازی | لمینت‌کاران و سازندگان فایبرگلاس | قالب‌سازان و ماهیچه‌سازان ریخته‌گری | شیشه‌گران، قالب‌سازان، خم‌کاران و پرداخت‌کاران شیشه | کارگران سنگ‌زنی و پولیش دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای سنگ‌زنی، لپینگ، پولیش و پرداخت فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان دستگاه | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک | کارگران رنگ‌آمیزی، پوشش‌دهی و تزیین | الگوسازان فلز و پلاستیک | سفالگران، تولیدی | تعمیرکاران مواد نسوز، به جز بناها | سنگ‌تراشان و قلم‌زنان سنگ، تولیدی | سازندگان و مونتاژکنندگان سازه‌های فلزی | تایر سازان | قالب‌سازان و ابزارسازان | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های چوب‌بری، به جز اره‌کشی</t>
+          <t>اپراتورها و متصدیان ماشین‌های اتصال چسبی | برش‌دهندگان و پرداخت‌کاران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن، شکل‌دهی، پرس و متراکم‌سازی | لمینت‌کاران و سازندگان فایبرگلاس | قالب‌سازان و ماهیچه‌سازان کارگاه ریخته‌گری | شیشه‌گران، قالب‌سازان، خم‌کاران و پرداخت‌کاران شیشه | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و صیقل‌کاری فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاست | کارگران نقاشی، پوشش‌دهی و تزیین | الگوسازان فلز و پلاستیک | سفالگران، تولیدی | تعمیرکاران مواد نسوز، به جز بناهای آجرکار | سنگ‌تراشان و قلم‌زنان سنگ، تولیدی | سازندگان و مونتاژکاران فلزات سازه‌ای | تایر سازان | سازندگان ابزار و قالب | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -684,22 +684,22 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ریاضیات | تولید و فرآوری | مکانیک | زبان انگلیسی | مدیریت و سازماندهی | طراحی | آموزش و پرورش</t>
+          <t>ریاضیات | تولید و فرآوری | مکانیک | زبان انگلیسی | مدیریت و اداره | طراحی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ثبات بازو-دست | بینایی نزدیک | چالاکی دست | دقت کنترل | چالاکی انگشتان | قدرت تنه | انعطاف‌پذیری بدنی | تجسم فضایی | هماهنگی چند عضو | تشخیص گفتار | قدرت ایستا | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال قیاسی | حساسیت به مشکل | استدلال استقرایی | بیان شفاهی | درک شفاهی</t>
+          <t>ثبات دست و بازو | بینایی نزدیک | مهارت دستی | دقت کنترل | مهارت انگشتان | قدرت تنه | انعطاف‌پذیری دامنه حرکت | تجسم | هماهنگی چند عضو | تشخیص گفتار | قدرت ایستا | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال قیاسی | حساسیت به مسئله | استدلال استقرایی | بیان شفاهی | درک شفاهی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان به صورت ایستاده | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض صداها و سطوح نویز مزاحم یا ناراحت‌کننده | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | اهمیت دقیق یا بی‌نقص بودن | بحث‌های چهره به چهره با افراد و درون تیم‌ها | صرف زمان برای انجام حرکات تکراری | فشار زمانی | تعیین وظایف، اولویت‌ها و اهداف | سلامت و ایمنی سایر کارگران | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای خم شدن یا پیچاندن بدن | پیامد خطا</t>
+          <t>صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای ایستادن | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | اهمیت دقیق یا درست بودن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای انجام حرکات تکراری | فشار زمانی | تعیین وظایف، اولویت‌ها و اهداف | سلامت و ایمنی سایر کارکنان | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای خم کردن یا چرخاندن بدن | پیامد خطا</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>بناها و بلوک‌چین‌ها | کابینت‌سازان و نجاران کارگاهی | سیمان‌کاران و پرداخت‌کاران بتن | برش‌کاران و آرایش‌دهندگان دستی | تیزاب‌کاران و حکاکان | پرداخت‌کاران مبلمان | کارگران سنگ‌زنی و پولیش دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای سنگ‌زنی، لپینگ، پولیش و پرداخت فلز و پلاستیک | جواهرسازان و کارگران سنگ‌ها و فلزات قیمتی | کارگران چیدمان و علامت‌گذاری فلز و پلاستیک | قالب‌سازان، شکل‌دهندگان و ریخته‌گران به جز فلز و پلاستیک | کارگران رنگ‌آمیزی، پوشش‌دهی و تزیین | الگوسازان چوب | شکاف‌دهندگان سنگ، معدن | سنگ‌تراشان | سازندگان و مونتاژکنندگان سازه‌های فلزی | کارگران و پرداخت‌کاران ترازو | کاشی‌کاران و سنگ‌کاران | تیزکنندگان و فیلرکنندگان ابزار و سنگ‌ساب‌ها | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های چوب‌بری، به جز اره‌کشی</t>
+          <t>بنّایان آجرکار و بلوک‌کار | کابینت‌سازان و نجاران نیمکت | بنّایان سیمان‌کار و پرداخت‌کاران بتن | برش‌دهندگان و پرداخت‌کاران دستی | حکاکان و تیزاب‌کاران | پرداخت‌کاران مبلمان | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و صیقل‌کاری فلز و پلاستیک | جواهرسازان و کارگران سنگ‌ها و فلزات قیمتی | کارگران شابلون‌زنی، فلز و پلاستیک | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | کارگران نقاشی، پوشش‌دهی و تزیین | الگوسازان چوب | سنگ‌شکنان معدن | بنّایان سنگ‌کار | سازندگان و مونتاژکاران فلزات سازه‌ای | کارگران و پرداخت‌کاران ترازو | کاشی‌کاران و سنگ‌کاران | سنگ‌زنان، سوهان‌کاران و تیزکنندگان ابزار | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,27 +736,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>مانیتورینگ | تفکر انتقادی | گوش دادن فعال | درک مطلب خواندن</t>
+          <t>نظارت | تفکر انتقادی | گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | طراحی | مکانیک | خدمات مشتریان و پرسنل | مهندسی و فناوری | ریاضیات | زبان انگلیسی</t>
+          <t>تولید و فرآوری | طراحی | مکانیک | خدمات مشتری و شخصی | مهندسی و فناوری | ریاضیات | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | ثبات بازو-دست | دقت کنترل | زمان عکس‌العمل | تشخیص رنگ بصری | تجسم فضایی | چالاکی دست | چالاکی انگشتان | توجه انتخابی | کنترل نرخ | هماهنگی چند عضو | سرعت ادراکی | قدرت تنه | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | حساسیت به مشکل | درک شفاهی</t>
+          <t>بینایی نزدیک | ثبات دست و بازو | دقت کنترل | زمان عکس‌العمل | تشخیص رنگ بصری | تجسم | مهارت دستی | مهارت انگشتان | توجه انتخابی | کنترل نرخ | هماهنگی چند عضو | سرعت ادراکی | قدرت تنه | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | درک شفاهی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>قرار گرفتن در معرض سوختگی‌های جزئی، برش‌ها، گازگرفتگی‌ها یا نیش‌ها | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض صداها و سطوح نویز مزاحم یا ناراحت‌کننده | اهمیت دقیق یا بی‌نقص بودن | بحث‌های چهره به چهره با افراد و درون تیم‌ها | فراوانی تصمیم‌گیری | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | آزادی در تصمیم‌گیری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض تجهیزات خطرناک | تاثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای انجام حرکات تکراری | داخل ساختمان، بدون محیط کنترل‌شده | صرف زمان به صورت ایستاده | پیامد خطا | سرعت تعیین‌شده توسط سرعت تجهیزات | نزدیکی فیزیکی</t>
+          <t>قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | اهمیت دقیق یا درست بودن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فراوانی تصمیم‌گیری | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | آزادی در تصمیم‌گیری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض تجهیزات خطرناک | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای انجام حرکات تکراری | محیط داخلی، بدون کنترل شرایط محیطی | صرف زمان برای ایستادن | پیامد خطا | سرعت تعیین‌شده توسط سرعت تجهیزات | نزدیکی فیزیکی</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و اسلایس | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکسترود و فرم‌دهی الیاف مصنوعی و شیشه | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکسترود، فرم‌دهی، پرس و متراکم‌سازی | کارگران سنگ‌زنی و پولیش دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای سنگ‌زنی، لپینگ، پولیش و پرداخت فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان تجهیزات عملیات حرارتی فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای تراش فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان دستگاه | اپراتورها و متصدیان کوره‌های تصفیه فلز | مدل‌سازان فلز و پلاستیک | قالب‌سازان، شکل‌دهندگان و ریخته‌گران به جز فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک | تکنسین‌های آزمایشگاه چشم‌پزشکی | سنگ‌تراشان و قلم‌زنان سنگ، تولیدی | سازندگان و مونتاژکنندگان سازه‌های فلزی | قالب‌سازان و ابزارسازان | جوشکاران، برش‌کاران، لحیم‌کاران نرم و سخت | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های جوشکاری، لحیم‌کاری نرم و سخت | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های چوب‌بری، به جز اره‌کشی</t>
+          <t>تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش، پانچ و پرس، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن، شکل‌دهی، پرس و متراکم‌سازی | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و صیقل‌کاری فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان تجهیزات عملیات حرارتی، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات تراشکاری فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | اپراتورها و متصدیان کوره تصفیه فلز | مدل‌سازان فلز و پلاستیک | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاست | تکنسین‌های آزمایشگاه چشم‌پزشکی | سنگ‌تراشان و قلم‌زنان سنگ، تولیدی | سازندگان و مونتاژکاران فلزات سازه‌ای | سازندگان ابزار و قالب | جوشکاران، برش‌کاران، لحیم‌کاران نرم و لحیم‌کاران سخت | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های جوشکاری، لحیم‌کاری نرم و لحیم‌کاری سخت | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,27 +793,27 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | گوش دادن فعال | مانیتورینگ</t>
+          <t>تفکر انتقادی | گوش دادن فعال | نظارت</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>هنرهای زیبا | تولید و فرآوری | طراحی | خدمات مشتریان و پرسنل | شیمی | مدیریت و سازماندهی | فروش و بازاریابی</t>
+          <t>هنرهای زیبا | تولید و فرآوری | طراحی | خدمات مشتری و شخصی | شیمی | مدیریت و اداره | فروش و بازاریابی</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>ثبات بازو-دست | چالاکی دست | چالاکی انگشتان | دقت کنترل | بینایی نزدیک | تجسم فضایی | هماهنگی چند عضو | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال قیاسی | اصالت | استدلال استقرایی | حساسیت به مشکل | روان بودن ایده‌ها | بیان شفاهی | درک شفاهی | تشخیص گفتار | تشخیص رنگ بصری | کنترل نرخ</t>
+          <t>ثبات دست و بازو | مهارت دستی | مهارت انگشتان | دقت کنترل | بینایی نزدیک | تجسم | هماهنگی چند عضو | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال قیاسی | اصالت | استدلال استقرایی | حساسیت به مسئله | روانی ایده‌ها | بیان شفاهی | درک شفاهی | تشخیص گفتار | تشخیص رنگ بصری | کنترل نرخ</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>آزادی در تصمیم‌گیری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | تعیین وظایف، اولویت‌ها و اهداف | تعامل با مشتریان خارجی یا عموم مردم به طور کلی | بحث‌های چهره به چهره با افراد و درون تیم‌ها | تاثیر تصمیمات بر همکاران یا نتایج شرکت | قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای انجام حرکات تکراری | فراوانی تصمیم‌گیری | اهمیت تکرار وظایف یکسان | اهمیت دقیق یا بی‌نقص بودن | ایمیل | داخل ساختمان، با محیط کنترل‌شده | ارتباط با دیگران | مکالمات تلفنی</t>
+          <t>آزادی در تصمیم‌گیری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | تعیین وظایف، اولویت‌ها و اهداف | تعامل با مشتریان خارجی یا عموم مردم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تأثیر تصمیمات بر همکاران یا نتایج شرکت | قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای انجام حرکات تکراری | فراوانی تصمیم‌گیری | اهمیت تکرار وظایف یکسان | اهمیت دقیق یا درست بودن | ایمیل | محیط داخلی، دارای کنترل شرایط محیطی | ارتباط با دیگران | مکالمات تلفنی</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>هنرمندان صنایع دستی | تیزاب‌کاران و حکاکان | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های فورج فلز و پلاستیک | قالب‌سازان و ماهیچه‌سازان ریخته‌گری | پرداخت‌کاران مبلمان | شیشه‌گران، قالب‌سازان، خم‌کاران و پرداخت‌کاران شیشه | کارگران سنگ‌زنی و پولیش دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای سنگ‌زنی، لپینگ، پولیش و پرداخت فلز و پلاستیک | جواهرسازان و کارگران سنگ‌ها و فلزات قیمتی | مدل‌سازان چوب | قالب‌سازان، شکل‌دهندگان و ریخته‌گران به جز فلز و پلاستیک | کارگران رنگ‌آمیزی، پوشش‌دهی و تزیین | الگوسازان فلز و پلاستیک | الگوسازان چوب | ریزندگان و ریخته‌گران فلز | تعمیرکاران مواد نسوز، به جز بناها | دوزندگان دستی | سنگ‌تراشان و قلم‌زنان سنگ، تولیدی | سازندگان و مونتاژکنندگان سازه‌های فلزی | تیزکنندگان و فیلرکنندگان ابزار و سنگ‌ساب‌ها</t>
+          <t>هنرمندان صنایع دستی | حکاکان و تیزاب‌کاران | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فورج، فلز و پلاستیک | قالب‌سازان و ماهیچه‌سازان کارگاه ریخته‌گری | پرداخت‌کاران مبلمان | شیشه‌گران، قالب‌سازان، خم‌کاران و پرداخت‌کاران شیشه | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و صیقل‌کاری فلز و پلاستیک | جواهرسازان و کارگران سنگ‌ها و فلزات قیمتی | مدل‌سازان چوب | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | کارگران نقاشی، پوشش‌دهی و تزیین | الگوسازان فلز و پلاستیک | الگوسازان چوب | ریزندگان و ریخته‌گران فلز | تعمیرکاران مواد نسوز، به جز بناهای آجرکار | دوزندگان دستی | سنگ‌تراشان و قلم‌زنان سنگ، تولیدی | سازندگان و مونتاژکاران فلزات سازه‌ای | سنگ‌زنان، سوهان‌کاران و تیزکنندگان ابزار</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -845,32 +845,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Adobe Acrobat | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Word | Objectif Lune PrintShop Mail | Quark enterprise publishing software | Virtual Systems Mail-Shop</t>
+          <t>Adobe Acrobat | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Word | Objectif Lune PrintShop Mail | نرم‌افزار نشر سازمانی Quark | Virtual Systems Mail-Shop</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>مانیتورینگ | تفکر انتقادی | سخن گفتن | گوش دادن فعال</t>
+          <t>نظارت | تفکر انتقادی | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | مکانیک | ریاضیات | خدمات مشتریان و پرسنل | زبان انگلیسی</t>
+          <t>تولید و فرآوری | مکانیک | ریاضیات | خدمات مشتری و شخصی | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | دقت کنترل | حساسیت به مشکل | ثبات بازو-دست | چالاکی انگشتان | چالاکی دست | توجه انتخابی | ترتیب‌دهی اطلاعات | بیان شفاهی | درک شفاهی | زمان عکس‌العمل | کنترل نرخ | استدلال قیاسی</t>
+          <t>بینایی نزدیک | دقت کنترل | حساسیت به مسئله | ثبات دست و بازو | مهارت انگشتان | مهارت دستی | توجه انتخابی | ترتیب‌دهی اطلاعات | بیان شفاهی | درک شفاهی | زمان عکس‌العمل | کنترل نرخ | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>قرار گرفتن در معرض صداها و سطوح نویز مزاحم یا ناراحت‌کننده | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | بحث‌های چهره به چهره با افراد و درون تیم‌ها | صرف زمان به صورت ایستاده | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | فراوانی تصمیم‌گیری | سلامت و ایمنی سایر کارگران | فشار زمانی | تاثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق یا بی‌نقص بودن | سرعت تعیین‌شده توسط سرعت تجهیزات | قرار گرفتن در معرض تجهیزات خطرناک | قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای انجام حرکات تکراری | داخل ساختمان، بدون محیط کنترل‌شده | سطح رقابت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | صرف زمان برای خم شدن یا پیچاندن بدن</t>
+          <t>قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای ایستادن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | فراوانی تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | فشار زمانی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق یا درست بودن | سرعت تعیین‌شده توسط سرعت تجهیزات | قرار گرفتن در معرض تجهیزات خطرناک | قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای انجام حرکات تکراری | محیط داخلی، بدون کنترل شرایط محیطی | سطح رقابت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | صرف زمان برای خم کردن یا چرخاندن بدن</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان دستگاه‌های اتصال چسبی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و اسلایس | تنظیم‌کنندگان, اپراتورها و متصدیان دستگاه‌های برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکسترود و کشش فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکسترود و فرم‌دهی الیاف مصنوعی و شیشه | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکسترود، فرم‌دهی، پرس و متراکم‌سازی | کارگران سنگ‌زنی و پولیش دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای سنگ‌زنی، لپینگ، پولیش و پرداخت فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تغذیه‌کنندگان و تخلیه‌کنندگان دستگاه | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های فرز و صفحه تراش فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای چندگانه فلز و پلاستیک | اپراتورها و متصدیان دستگاه‌های بسته‌بندی و پرکن | کارگران صحافی و پرداخت چاپ | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های نورد فلز و پلاستیک | اپراتورهای ماشین دوخت | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش منسوجات | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های سیم‌پیچی، تابندگی و کشش منسوجات | تیزکنندگان و فیلرکنندگان ابزار و سنگ‌ساب‌ها | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های چوب‌بری، به جز اره‌کشی</t>
+          <t>اپراتورها و متصدیان ماشین‌های اتصال چسبی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش، پانچ و پرس، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکسترود و کشش، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن، شکل‌دهی، پرس و متراکم‌سازی | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و صیقل‌کاری فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات فرزکاری و صفحه‌تراشی فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان چندین ماشین‌ابزار، فلز و پلاستیک | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | کارکنان صحافی و پرداخت چاپ | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های نورد، فلز و پلاستیک | اپراتورهای چرخ خیاطی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین برش منسوجات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین بوبین‌پیچی، تابندگی و کشش منسوجات | سنگ‌زنان، سوهان‌کاران و تیزکنندگان ابزار | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,27 +907,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>مانیتورینگ | تفکر انتقادی | گوش دادن فعال</t>
+          <t>نظارت | تفکر انتقادی | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | مدیریت و سازماندهی | مکانیک</t>
+          <t>تولید و فرآوری | مدیریت و اداره | مکانیک</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>چالاکی دست | ثبات بازو-دست | دقت کنترل | هماهنگی چند عضو | قدرت تنه | کنترل نرخ | چالاکی انگشتان | بینایی نزدیک | انعطاف‌پذیری بدنی | قدرت ایستا | زمان عکس‌العمل | توجه انتخابی | حساسیت به مشکل | درک شفاهی | استقامت بدنی | تشخیص گفتار | توجه شنیداری</t>
+          <t>مهارت دستی | ثبات دست و بازو | دقت کنترل | هماهنگی چند عضو | قدرت تنه | کنترل نرخ | مهارت انگشتان | بینایی نزدیک | انعطاف‌پذیری دامنه حرکت | قدرت ایستا | زمان عکس‌العمل | توجه انتخابی | حساسیت به مسئله | درک شفاهی | استقامت | تشخیص گفتار | توجه شنیداری</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>صرف زمان به صورت ایستاده | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض صداها و سطوح نویز مزاحم یا ناراحت‌کننده | قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای خم شدن یا پیچاندن بدن | بحث‌های چهره به چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض تجهیزات خطرناک | فشار زمانی | قرار گرفتن در معرض شرایط خطرناک | ارتباط با دیگران | اهمیت تکرار وظایف یکسان | قرار گرفتن در معرض سوختگی‌های جزئی، برش‌ها، گازگرفتگی‌ها یا نیش‌ها | سرعت تعیین‌شده توسط سرعت تجهیزات | تاثیر تصمیمات بر همکاران یا نتایج شرکت | پیامدهای کاری و نتایج سایر کارگران | اهمیت دقیق یا بی‌نقص بودن | نزدیکی فیزیکی</t>
+          <t>صرف زمان برای ایستادن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای خم کردن یا چرخاندن بدن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض تجهیزات خطرناک | فشار زمانی | قرار گرفتن در معرض شرایط خطرناک | ارتباط با دیگران | اهمیت تکرار وظایف یکسان | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | سرعت تعیین‌شده توسط سرعت تجهیزات | تأثیر تصمیمات بر همکاران یا نتایج شرکت | پیامدهای کاری و نتایج سایر کارکنان | اهمیت دقیق یا درست بودن | نزدیکی فیزیکی</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | تعمیرکاران بدنه خودرو و موارد مرتبط | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های پوشش‌دهی، رنگ‌آمیزی و اسپری | مونتاژکنندگان موتور و سایر ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکسترود و کشش فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکسترود و فرم‌دهی الیاف مصنوعی و شیشه | لمینت‌کاران و سازندگان فایبرگلاس | قالب‌سازان و ماهیچه‌سازان ریخته‌گری | کارگران سنگ‌زنی و پولیش دستی | مکانیک‌های ماشین‌آلات صنعتی | کارگران عایق‌کاری کف، سقف و دیوار | کارگران عایق‌کاری مکانیکی | قالب‌سازان، شکل‌دهندگان و ریخته‌گران به جز فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های آبکاری فلز و پلاستیک | تعمیرکاران واگن‌های ریلی | اپراتورها و متصدیان دستگاه‌های کفش‌دوزی | سازندگان و مونتاژکنندگان سازه‌های فلزی | تعمیرکاران و تعویض‌کنندگان تایر | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های جوشکاری، لحیم‌کاری نرم و سخت</t>
+          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | تعمیرکنندگان بدنه خودرو و موارد مرتبط | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های پوشش‌دهی، نقاشی و اسپری | مونتاژکاران موتور و سایر ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکسترود و کشش، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه | لمینت‌کاران و سازندگان فایبرگلاس | قالب‌سازان و ماهیچه‌سازان کارگاه ریخته‌گری | کارگران سنگ‌زنی و پرداخت دستی | مکانیک‌های ماشین‌آلات صنعتی | کارگران عایق‌کاری کف، سقف و دیوار | کارگران عایق‌کاری، مکانیکی | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاست | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های آبکاری، فلز و پلاستیک | تعمیرکنندگان واگن‌های ریلی | اپراتورها و متصدیان ماشین‌آلات کفش‌سازی | سازندگان و مونتاژکاران فلزات سازه‌ای | تعمیرکنندگان و تعویض‌کنندگان لاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های جوشکاری، لحیم‌کاری نرم و لحیم‌کاری سخت</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>مانیتورینگ | گوش دادن فعال | سخن گفتن | تفکر انتقادی | درک مطلب خواندن</t>
+          <t>نظارت | گوش دادن فعال | سخن گفتن | تفکر انتقادی | درک مطلب</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -974,17 +974,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | دقت کنترل | قدرت ایستا | قدرت تنه | چالاکی دست | هماهنگی چند عضو | چالاکی انگشتان | ثبات بازو-دست | ترتیب‌دهی اطلاعات | حساسیت به مشکل | انعطاف‌پذیری بدنی | استقامت بدنی | سرعت ادراکی | بیان شفاهی | درک شفاهی</t>
+          <t>بینایی نزدیک | دقت کنترل | قدرت ایستا | قدرت تنه | مهارت دستی | هماهنگی چند عضو | مهارت انگشتان | ثبات دست و بازو | ترتیب‌دهی اطلاعات | حساسیت به مسئله | انعطاف‌پذیری دامنه حرکت | استقامت | سرعت ادراکی | بیان شفاهی | درک شفاهی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | بحث‌های چهره به چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض صداها و سطوح نویز مزاحم یا ناراحت‌کننده | فشار زمانی | صرف زمان برای انجام حرکات تکراری | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا بی‌نقص بودن | سرعت تعیین‌شده توسط سرعت تجهیزات | ارتباط با دیگران | صرف زمان به صورت ایستاده | داخل ساختمان، بدون محیط کنترل‌شده | آزادی در تصمیم‌گیری | صرف زمان برای خم شدن یا پیچاندن بدن | فراوانی تصمیم‌گیری | قرار گرفتن در معرض آلاینده‌ها</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | فشار زمانی | صرف زمان برای انجام حرکات تکراری | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن | سرعت تعیین‌شده توسط سرعت تجهیزات | ارتباط با دیگران | صرف زمان برای ایستادن | محیط داخلی، بدون کنترل شرایط محیطی | آزادی در تصمیم‌گیری | صرف زمان برای خم کردن یا چرخاندن بدن | فراوانی تصمیم‌گیری | قرار گرفتن در معرض آلاینده‌ها</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان دستگاه‌های اتصال چسبی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و اسلایس | کارگران سنگ‌زنی و پولیش دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای سنگ‌زنی، لپینگ، پولیش و پرداخت فلز و پلاستیک | کمک‌کاران--بناها، بلوک‌چین‌ها، سنگ‌تراشان و کاشی‌کاران و مرمرکاران | کمک‌کاران--نجاران | کمک‌کاران--برق‌کاران | کمک‌کاران--کارگران استخراج | کمک‌کاران--کارگران نصب، نگهداری و تعمیرات | کمک‌کاران--نقاشان، کاغذدیوارکن‌ها، گچ‌کاران و سیمان‌کاران | کمک‌کاران--لوله‌کشان، لوله‌کش‌های صنعتی و بخار | کارگران و جابجا کنندگان دستی بار، کالا و مواد | کارگران لباسشویی و خشک‌شویی | تغذیه‌کنندگان و تخلیه‌کنندگان دستگاه | کارگران نگهداری ماشین‌آلات | اپراتورها و متصدیان دستگاه‌های بسته‌بندی و پرکن | بسته‌بندندگان دستی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های تولید محصولات کاغذی | تیزکنندگان و فیلرکنندگان ابزار و سنگ‌ساب‌ها | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های چوب‌بری، به جز اره‌کشی</t>
+          <t>اپراتورها و متصدیان ماشین‌های اتصال چسبی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و صیقل‌کاری فلز و پلاستیک | دستیاران--بناهای آجر، بلوک، سنگ و نصابان کاشی و مرمر | دستیاران--نجاران | دستیاران--برق‌کاران | دستیاران--کارگران استخراج | دستیاران--کارگران نصب، نگهداری و تعمیرات | دستیاران--نقاشان، کاغذدیواری‌کن‌ها، گچ‌کاران و بناهای گچ‌بری | دستیاران--لوله‌کشان، لوله‌کشان صنعتی و بخار | کارگران و جابجا‌کنندگان دستی بار، کالا و مواد | کارکنان خشک‌شویی و لباس‌شویی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | کارگران تعمیر و نگهداری ماشین‌آلات | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | بسته‌بندهای دستی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های تولید محصولات کاغذی | سنگ‌زنان، سوهان‌کاران و تیزکنندگان ابزار | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1016,12 +1016,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | نرم‌افزار کنترل‌کننده منطقی قابل برنامه‌ریزی PLC | نرم‌افزار کنترل فرآیند آماری SPC | نرم‌افزار برنامه‌ریزی مواد مورد نیاز MRP | سیستم مدیریت کامپیوتری نگهداری و تعمیرات CMMS | Microsoft Excel | Microsoft Word | نرم‌افزار ایمیل | سیستم‌های مدیریت موجودی | سیستم برنامه‌ریزی منابع سازمانی ERP | نرم‌افزار پایگاه داده | نرم‌افزار SAP</t>
+          <t>نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | نرم‌افزار کنترل‌کننده منطقی قابل برنامه‌ریزی PLC | نرم‌افزار کنترل فرآیند آماری SPC | نرم‌افزار برنامه‌ریزی نیازمندی‌های مواد MRP | سیستم مدیریت نگهداری کامپیوتری CMMS | Microsoft Excel | Microsoft Word | نرم‌افزار ایمیل | سیستم‌های مدیریت موجودی | سیستم برنامه‌ریزی منابع سازمانی ERP | نرم‌افزار پایگاه داده | نرم‌افزار SAP</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>مانیتورینگ | گوش دادن فعال | تفکر انتقادی | درک مطلب خواندن | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1031,17 +1031,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>چالاکی دست | چالاکی انگشتان | ثبات بازو-دست | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | قدرت تنه | استقامت بدنی | بینایی نزدیک | بینایی دور | درک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری بدنی | زمان عکس‌العمل | حساسیت به مشکل | درک شفاهی | توجه انتخابی</t>
+          <t>مهارت دستی | مهارت انگشتان | ثبات دست و بازو | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | قدرت تنه | استقامت | بینایی نزدیک | بینایی دور | درک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری دامنه حرکت | زمان عکس‌العمل | حساسیت به مسئله | درک شفاهی | توجه انتخابی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>داخل ساختمان، بدون محیط کنترل‌شده | صرف زمان به صورت ایستاده | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض صداها و سطوح نویز مزاحم یا ناراحت‌کننده | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض تجهیزات خطرناک | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای خم شدن یا پیچاندن بدن | نزدیکی فیزیکی | سرعت تعیین‌شده توسط سرعت تجهیزات | سلامت و ایمنی سایر کارگران | پیامد خطا | میزان اتوماسیون | اهمیت تکرار وظایف یکسان | بحث‌های چهره به چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا بی‌نقص بودن</t>
+          <t>محیط داخلی، بدون کنترل شرایط محیطی | صرف زمان برای ایستادن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض تجهیزات خطرناک | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای خم کردن یا چرخاندن بدن | نزدیکی فیزیکی | سرعت تعیین‌شده توسط سرعت تجهیزات | سلامت و ایمنی سایر کارکنان | پیامد خطا | میزان خودکارسازی | اهمیت تکرار وظایف یکسان | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>کمک‌کاران--کارگران تولید | مونتاژکنندگان تیمی | مونتاژکنندگان و سازندگان، سایر موارد | بازرسان، آزمایش‌کنندگان، سورترها، نمونه‌برداران و وزن‌کنندگان | اپراتورها و متصدیان دستگاه‌های بسته‌بندی و پرکن | بسته‌بندندگان دستی | تغذیه‌کنندگان و تخلیه‌کنندگان دستگاه | برش‌کاران و آرایش‌دهندگان دستی | کارگران سنگ‌زنی و پولیش دستی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های مخلوط‌کن و ترکیب‌کننده | اپراتورها و متصدیان کوره، کوره پخت، فر، خشک‌کن و دیگ بخار | اپراتورها و متصدیان تجهیزات تمیزکاری، شستشو و اسیدشویی فلزات | اپراتورها و متصدیان دستگاه‌های اتصال چسبی | کارگران رنگ‌آمیزی، پوشش‌دهی و تزیین | اپراتورهای ابزار کنترل عددی کامپیوتری | ماشین‌کاران | مکانیک‌های ماشین‌آلات صنعتی | سرپرستان خط اول کارگران تولید و عملیاتی | اپراتورهای تراکتور و کامیون صنعتی | کارگران و جابجا کنندگان دستی بار، کالا و مواد</t>
+          <t>کمک‌کاران--کارگران تولید | مونتاژکاران تیمی | مونتاژکاران و سازندگان، سایر موارد | بازرسان، آزمایش‌کنندگان، سورترها، نمونه‌برداران و توزین‌کنندگان | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | بسته‌بندهای دستی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | برش‌دهندگان و پرداخت‌کاران دستی | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های مخلوط‌کن و ترکیب‌کننده | اپراتورها و متصدیان کوره، کوره پخت، فر، خشک‌کن و دیگ بخار | اپراتورها و متصدیان تجهیزات تمیزکاری، شستشو و اسیدشویی فلزات | اپراتورها و متصدیان ماشین‌های اتصال چسبی | کارگران نقاشی، پوشش‌دهی و تزیین | اپراتورهای ابزار کنترل عددی کامپیوتری | ماشین‌کاران | مکانیک‌های ماشین‌آلات صنعتی | سرپرستان رده اول کارگران تولید و بهره‌برداری | اپراتورهای تراکتور و کامیون صنعتی | کارگران و جابجا‌کنندگان دستی بار، کالا و مواد</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0094_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0094_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | نظارت | سخن گفتن | یادگیری فعال | شنیدن فعال | درک مطلب</t>
+          <t>تفکر انتقادی | نظارت | سخن گفتن | یادگیری فعال | گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | مکانیک | زبان انگلیسی | تولید مواد غذایی | مدیریت و امور اداری | ریاضیات | ایمنی و امنیت عمومی | آموزش و تدریس</t>
+          <t>تولید و فرآوری | مکانیک | زبان انگلیسی | تولید مواد غذایی | مدیریت و اداره | ریاضیات | ایمنی و امنیت عمومی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>دید نزدیک | حساسیت به مسئله | استدلال قیاسی | سرعت ادراک | ثبات دست و بازو | قدرت بالاتنه | قدرت ایستا | زمان واکنش | دقت در کنترل | چابکی انگشتان | چابکی دستی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | کنترل نرخ | هماهنگی اندام‌ها | انعطاف‌پذیری در طبقه‌بندی | مرتب‌سازی اطلاعات | استدلال استقرایی | بیان کتبی | درک کتبی | درک شفاهی</t>
+          <t>بینایی نزدیک | حساسیت به مسئله | استدلال قیاسی | سرعت ادراکی | ثبات دست و بازو | قدرت تنه | قدرت ایستا | زمان عکس‌العمل | دقت کنترل | مهارت انگشتان | مهارت دستی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | کنترل نرخ | هماهنگی چند عضو | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال استقرایی | بیان کتبی | درک کتبی | درک شفاهی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>تکنسین‌های نیروگاه‌های زیست‌توده | اپراتورها و متصدیان تجهیزات شستشو و اسیدشویی فلزات | تنظیم‌کنندگان و اپراتورهای ماشین‌های خردایش، سنگ‌زنی و پرداخت | تنظیم‌کنندگان و اپراتورهای ماشین‌های اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه‌ای | تنظیم‌کنندگان و اپراتورهای ماشین‌های اکستروژن، شکل‌دهی، پرس و فشرده‌سازی | متصدیان بچ‌سازی و فرمولاسیون مواد غذایی | اپراتورها و متصدیان ماشین‌های پخت صنعتی غذا | اپراتورها و متصدیان تجهیزات تفت دادن، پخت و خشک‌کردن مواد غذایی و تنباکو | اپراتورها و متصدیان کوره‌ها، خشک‌کن‌ها و دیگ‌های صنعتی | اپراتورهای کمپرسور گاز و ایستگاه‌های پمپاژ گاز | تنظیم‌کنندگان و اپراتورهای تجهیزات عملیات حرارتی فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | اپراتورها و متصدیان کوره‌های تصفیه و ذوب فلز | تنظیم‌کنندگان و اپراتورهای ماشین‌های اختلاط و ترکیب مواد | تنظیم‌کنندگان و اپراتورهای ماشین‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | تنظیم‌کنندگان و اپراتورهای ماشین‌های تولید محصولات کاغذی | تنظیم‌کنندگان و اپراتورهای ماشین‌های نورد فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های جداسازی، فیلتراسیون، شفاف‌سازی و تقطیر | مهندسان تاسیسات ثابت و اپراتورهای دیگ بخار</t>
+          <t>تکنسین‌های نیروگاه زیست‌توده | اپراتورها و متصدیان تجهیزات شست‌وشو، نظافت و چربی‌زدایی فلزات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات خردایش، آسیاب و پرداخت | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه‌ای | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکستروژن، فرم‌دهی، پرس و تراکم مواد | تولیدکنندگان فرمولی و دسته‌ای مواد غذایی | اپراتورهای ماشین‌آلات پخت مواد غذایی | اپراتورهای ماشین‌آلات برشته‌کاری، پخت و خشک‌کن مواد غذایی و توتون | اپراتورها و متصدیان کوره‌ها، خشک‌کن‌ها و پاتیل‌های صنعتی | اپراتورهای ایستگاه پمپاژ و کمپرسور گاز | تنظیم‌کاران و اپراتورهای تجهیزات عملیات حرارتی فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | اپراتورها و متصدیان کوره‌های تصفیه و ذوب فلزات | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های مخلوط‌کن و ترکیب مواد | تنظیم‌کاران و اپراتورهای ماشین‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | تنظیم‌کنندگان و اپراتورهای ماشین‌های تولید محصولات کاغذی | تنظیم‌کنندگان و اپراتورهای ماشین‌های نورد فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، شفاف‌سازی، ترسیب و تقطیر | مهندسان تأسیسات و اپراتورهای دیگ‌بخار صنعتی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب | نظارت | تفکر انتقادی | سخن گفتن | شنیدن فعال</t>
+          <t>درک مطلب | نظارت | تفکر انتقادی | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | خدمات مشتریان و خدمات فردی | مکانیک | طراحی</t>
+          <t>تولید و فرآوری | خدمات مشتری و شخصی | مکانیک | طراحی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>دید نزدیک | ثبات دست و بازو | دقت در کنترل | درک شفاهی | بیان شفاهی | توجه انتخابی | چابکی دستی | چابکی انگشتان | وضوح گفتار | تشخیص گفتار | تجسم فضایی | حساسیت به مسئله | درک کتبی | انعطاف‌پذیری در طبقه‌بندی | مرتب‌سازی اطلاعات | استدلال استقرایی | استدلال قیاسی | روانی ایده‌ها</t>
+          <t>بینایی نزدیک | ثبات دست و بازو | دقت کنترل | درک شفاهی | بیان شفاهی | توجه انتخابی | مهارت دستی | مهارت انگشتان | وضوح گفتار | تشخیص گفتار | تجسم | حساسیت به مسئله | درک کتبی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال استقرایی | استدلال قیاسی | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>تنظیم‌کنندگان و اپراتورهای ماشین‌های پوشش‌دهی، رنگ‌کاری و اسپری | برشکاران دستی قطعات | تنظیم‌کنندگان و اپراتورهای ماشین‌های برش و اسلایسر | تنظیم‌کنندگان و اپراتورهای ماشین‌های برش، پانچ و پرس فلز و پلاستیک | الگوسازان پارچه و پوشاک | کارگران پرداخت‌کاری و سنگ‌زنی دستی | تنظیم‌کنندگان و اپراتورهای ماشین‌ابزارهای سنگ‌زنی، لپینگ و پولیش فلز و پلاستیک | طلاسازان و سازندگان مصنوعات قیمتی و فلزات گرانبها | نشانه‌گذاران و خط‌کشان خطوط برش قطعات فلزی و پلاستیکی | تنظیم‌کنندگان و اپراتورهای ماشین‌های فرز و رنده‌تراش فلز و پلاستیک | مدل‌سازان فلزی و پلاستیکی | قالب‌ریزان و شکل‌دهندگان مواد غیرفلزی و غیرپلاستیکی | تکنسین‌های آزمایشگاه اپتیک و ساخت عدسی | کارگران نقاشی صنعتی، پوشش‌دهی و تزیین | الگوسازان صنعتی فلز و پلاستیک | تکنسین‌ها و کارگران مراحل پیش از چاپ | اپراتورهای ماشین‌های چاپ صنعتی | سنگ‌تراشان و حکاکان سنگ در خطوط تولید | سنگ‌زن‌ها و تیزکاران ابزار صنعتی | قالب‌سازان و ابزارسازان صنعتی</t>
+          <t>تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های پوشش‌دهی، رنگ‌کاری و اسپری | برشکاران و پیرایشگران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | تنظیم‌کنندگان و اپراتورهای ماشین‌های برش، پانچ و پرس فلز و پلاستیک | الگوسازان پارچه و پوشاک | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | جواهرسازان و سازندگان مصنوعات فلزی و سنگ‌های قیمتی | خط‌کش‌ها و نشانه‌گذاران قطعات فلزی و پلاستیکی | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | مدل‌سازان فلز و پلاستیک | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | تکنسین‌های آزمایشگاه و کارگاه ساخت عینک و قطعات اپتیک | کارگران رنگ‌کاری، پوشش‌دهی و تزیین قطعات | الگوسازان فلز و پلاستیک | تکنسین‌ها و کارگران لیتوگرافی و پیش از چاپ | اپراتورهای ماشین‌های چاپ | سنگ‌تراشان و حکاکان صنعتی سنگ | سنگ‌زن‌ها، سوهان‌کاران و تیزکاران ابزار | قالب‌سازان و ابزارسازان صنعتی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | درک مطلب | سخن گفتن | ریاضیات</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن | ریاضیات</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | چابکی انگشتان | چابکی دستی | دقت در کنترل | دید نزدیک | هماهنگی اندام‌ها | توجه انتخابی | درک شفاهی | انعطاف‌پذیری گسترده بدن | مرتب‌سازی اطلاعات | استدلال استقرایی | استدلال قیاسی</t>
+          <t>ثبات دست و بازو | مهارت انگشتان | مهارت دستی | دقت کنترل | بینایی نزدیک | هماهنگی چند عضو | توجه انتخابی | درک شفاهی | انعطاف‌پذیری دامنه حرکت | ترتیب‌دهی اطلاعات | استدلال استقرایی | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان ماشین‌های اتصال چسبی | برشکاران دستی قطعات | تنظیم‌کنندگان و اپراتورهای ماشین‌های برش و اسلایسر | تنظیم‌کنندگان و اپراتورهای ماشین‌های اکستروژن، شکل‌دهی، پرس و فشرده‌سازی | سازندگان و لمینیت‌کاران قطعات فایبرگلاس | قالب‌سازان و ماهیچه‌سازان ریخته‌گری چدن و فولاد | دمندگان، قالب‌گیران، خم‌کاران و پرداخت‌کاران شیشه | کارگران پرداخت‌کاری و سنگ‌زنی دستی | تنظیم‌کنندگان و اپراتورهای ماشین‌ابزارهای سنگ‌زنی، لپینگ و پولیش فلز و پلاستیک | تغذیه‌کنندگان و متصدیان تخلیه دستگاه‌های صنعتی | تنظیم‌کنندگان و اپراتورهای ماشین‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک | کارگران نقاشی صنعتی، پوشش‌دهی و تزیین | الگوسازان صنعتی فلز و پلاستیک | سفالگران خطوط تولید | تعمیرکاران نسوزها و جداره‌های کوره | سنگ‌تراشان و حکاکان سنگ در خطوط تولید | سازندگان و مونتاژکاران اسکلت فلزی | سازندگان تایر خودرو | قالب‌سازان و ابزارسازان صنعتی | تنظیم‌کنندگان و اپراتورهای ماشین‌آلات چوب‌بری به‌جز اره</t>
+          <t>اپراتورها و متصدیان ماشین‌های چسب‌زنی و اتصال | برشکاران و پیرایشگران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکستروژن، فرم‌دهی، پرس و تراکم مواد | لایه‌نشانان و سازندگان فایبرگلاس | قالب‌گیران و ماهیچه‌سازان ریخته‌گری | دمندگان، قالب‌گیران، خم‌کاران و پرداخت‌کاران شیشه | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کاران و اپراتورهای ماشین‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک | کارگران رنگ‌کاری، پوشش‌دهی و تزیین قطعات | الگوسازان فلز و پلاستیک | سفالگران خطوط تولید و کارگاهی | تعمیرکاران و نسوزکاران مواد دیرگداز صنعتی | سنگ‌تراشان و حکاکان صنعتی سنگ | سازندگان و مونتاژکاران سازه‌های فلزی | سازندگان تایر | قالب‌سازان و ابزارسازان صنعتی | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,22 +674,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Corel Paint Shop Pro | نرم‌افزار مدیریت موجودی | نرم‌افزار ثبت ساعت کار | Microsoft Excel | Microsoft Word</t>
+          <t>Corel Paint Shop Pro | نرم‌افزار مدیریت موجودی | نرم‌افزار ثبت ساعت کار | Microsoft Excel | نرم‌افزار ثبت زمان</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال</t>
+          <t>تفکر انتقادی | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ریاضیات | تولید و فرآوری | مکانیک | زبان انگلیسی | مدیریت و امور اداری | طراحی | آموزش و تدریس</t>
+          <t>ریاضیات | تولید و فرآوری | مکانیک | زبان انگلیسی | مدیریت و اداره | طراحی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | دید نزدیک | چابکی دستی | دقت در کنترل | چابکی انگشتان | قدرت بالاتنه | انعطاف‌پذیری گسترده بدن | تجسم فضایی | هماهنگی اندام‌ها | تشخیص گفتار | قدرت ایستا | توجه انتخابی | انعطاف‌پذیری در طبقه‌بندی | مرتب‌سازی اطلاعات | استدلال قیاسی | حساسیت به مسئله | استدلال استقرایی | بیان شفاهی | درک شفاهی</t>
+          <t>ثبات دست و بازو | بینایی نزدیک | مهارت دستی | دقت کنترل | مهارت انگشتان | قدرت تنه | انعطاف‌پذیری دامنه حرکت | تجسم | هماهنگی چند عضو | تشخیص گفتار | قدرت ایستا | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال قیاسی | حساسیت به مسئله | استدلال استقرایی | بیان شفاهی | درک شفاهی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>بنایان و آجرچین‌ها | کابینت‌سازان و درودگران کارگاهی | سیمان‌کاران و پرداخت‌کاران بتن | برشکاران دستی قطعات | حکاکان و اسیدکاران | رنگ‌کاران و پرداخت‌کاران مبلمان | کارگران پرداخت‌کاری و سنگ‌زنی دستی | تنظیم‌کنندگان و اپراتورهای ماشین‌ابزارهای سنگ‌زنی، لپینگ و پولیش فلز و پلاستیک | طلاسازان و سازندگان مصنوعات قیمتی و فلزات گرانبها | نشانه‌گذاران و خط‌کشان خطوط برش قطعات فلزی و پلاستیکی | قالب‌ریزان و شکل‌دهندگان مواد غیرفلزی و غیرپلاستیکی | کارگران نقاشی صنعتی، پوشش‌دهی و تزیین | الگوسازان چوبی صنعتی | کارگران استخراج و شکافتن سنگ در معدن | سنگ‌چین‌ها و سنّت‌تراشان ساختمانی | سازندگان و مونتاژکاران اسکلت فلزی | نصابان و پرداخت‌کاران موزاییک درجا (ترازو) | کاشی‌کاران و سنگ‌کاران ساختمانی | سنگ‌زن‌ها و تیزکاران ابزار صنعتی | تنظیم‌کنندگان و اپراتورهای ماشین‌آلات چوب‌بری به‌جز اره</t>
+          <t>بنایان و سفت‌کاران ساختمان | کابینت‌سازان و نجاران کارگاهی | بتن‌ریزان و پرداخت‌کاران بتن | برشکاران و پیرایشگران دستی | حکاکان و اسیدکاران | پرداخت‌کاران و رنگ‌کاران چوب و مبلمان | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | جواهرسازان و سازندگان مصنوعات فلزی و سنگ‌های قیمتی | خط‌کش‌ها و نشانه‌گذاران قطعات فلزی و پلاستیکی | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | کارگران رنگ‌کاری، پوشش‌دهی و تزیین قطعات | الگوسازان چوب | سنگ‌شکنان و برش‌کاران سنگ معدن | سنگ‌کاران ساختمانی | سازندگان و مونتاژکاران سازه‌های فلزی | موزاییک‌کاران و پرداخت‌کاران terrazzo | کاشی‌کاران و سنگ‌کاران ظریف | سنگ‌زن‌ها، سوهان‌کاران و تیزکاران ابزار | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -731,22 +731,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>نرم‌افزار صدور فاکتور و صورت‌حساب | نرم‌افزار مدیریت موجودی | Microsoft Excel | Microsoft Outlook</t>
+          <t>نرم‌افزار صدور صورتحساب | نرم‌افزار مدیریت موجودی | Microsoft Excel | Microsoft Outlook</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>نظارت | تفکر انتقادی | شنیدن فعال | درک مطلب</t>
+          <t>نظارت | تفکر انتقادی | گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | طراحی | مکانیک | خدمات مشتریان و خدمات فردی | مهندسی و فناوری | ریاضیات | زبان انگلیسی</t>
+          <t>تولید و فرآوری | طراحی | مکانیک | خدمات مشتری و شخصی | مهندسی و فناوری | ریاضیات | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>دید نزدیک | ثبات دست و بازو | دقت در کنترل | زمان واکنش | تمایز رنگ‌ها | تجسم فضایی | چابکی دستی | چابکی انگشتان | توجه انتخابی | کنترل نرخ | هماهنگی اندام‌ها | سرعت ادراک | قدرت بالاتنه | انعطاف‌پذیری در طبقه‌بندی | مرتب‌سازی اطلاعات | حساسیت به مسئله | درک شفاهی</t>
+          <t>بینایی نزدیک | ثبات دست و بازو | دقت کنترل | زمان عکس‌العمل | تشخیص رنگ بصری | تجسم | مهارت دستی | مهارت انگشتان | توجه انتخابی | کنترل نرخ | هماهنگی چند عضو | سرعت ادراکی | قدرت تنه | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | درک شفاهی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>تنظیم‌کنندگان و اپراتورهای ماشین‌های برش و اسلایسر | تنظیم‌کنندگان و اپراتورهای ماشین‌های برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه‌ای | تنظیم‌کنندگان و اپراتورهای ماشین‌های اکستروژن، شکل‌دهی، پرس و فشرده‌سازی | کارگران پرداخت‌کاری و سنگ‌زنی دستی | تنظیم‌کنندگان و اپراتورهای ماشین‌ابزارهای سنگ‌زنی، لپینگ و پولیش فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای تجهیزات عملیات حرارتی فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های تراش فلز و پلاستیک | تغذیه‌کنندگان و متصدیان تخلیه دستگاه‌های صنعتی | اپراتورها و متصدیان کوره‌های تصفیه و ذوب فلز | مدل‌سازان فلزی و پلاستیکی | قالب‌ریزان و شکل‌دهندگان مواد غیرفلزی و غیرپلاستیکی | تنظیم‌کنندگان و اپراتورهای ماشین‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک | تکنسین‌های آزمایشگاه اپتیک و ساخت عدسی | سنگ‌تراشان و حکاکان سنگ در خطوط تولید | سازندگان و مونتاژکاران اسکلت فلزی | قالب‌سازان و ابزارسازان صنعتی | جوشکاران، برشکاران، لحیم‌کاران و برنج‌جوش‌ها | تنظیم‌کنندگان و اپراتورهای ماشین‌های جوشکاری و لحیم‌کاری | تنظیم‌کنندگان و اپراتورهای ماشین‌آلات چوب‌بری به‌جز اره</t>
+          <t>تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | تنظیم‌کنندگان و اپراتورهای ماشین‌های برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه‌ای | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکستروژن، فرم‌دهی، پرس و تراکم مواد | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | تنظیم‌کاران و اپراتورهای تجهیزات عملیات حرارتی فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌های تراشکاری فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | اپراتورها و متصدیان کوره‌های تصفیه و ذوب فلزات | مدل‌سازان فلز و پلاستیک | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | تنظیم‌کاران و اپراتورهای ماشین‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک | تکنسین‌های آزمایشگاه و کارگاه ساخت عینک و قطعات اپتیک | سنگ‌تراشان و حکاکان صنعتی سنگ | سازندگان و مونتاژکاران سازه‌های فلزی | قالب‌سازان و ابزارسازان صنعتی | جوشکاران، برشکاران و لحیم‌کاران صنعتی | تنظیم‌کاران و اپراتورهای دستگاه‌های جوشکاری و لحیم‌کاری | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال | نظارت</t>
+          <t>تفکر انتقادی | گوش دادن فعال | نظارت</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>هنرهای تجسمی | تولید و فرآوری | طراحی | خدمات مشتریان و خدمات فردی | شیمی | مدیریت و امور اداری | فروش و بازاریابی</t>
+          <t>هنرهای زیبا | تولید و فرآوری | طراحی | خدمات مشتری و شخصی | شیمی | مدیریت و اداره | فروش و بازاریابی</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | چابکی دستی | چابکی انگشتان | دقت در کنترل | دید نزدیک | تجسم فضایی | هماهنگی اندام‌ها | توجه انتخابی | انعطاف‌پذیری در طبقه‌بندی | مرتب‌سازی اطلاعات | استدلال قیاسی | اصالت و خلاقیت | استدلال استقرایی | حساسیت به مسئله | روانی ایده‌ها | بیان شفاهی | درک شفاهی | تشخیص گفتار | تمایز رنگ‌ها | کنترل نرخ</t>
+          <t>ثبات دست و بازو | مهارت دستی | مهارت انگشتان | دقت کنترل | بینایی نزدیک | تجسم | هماهنگی چند عضو | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال قیاسی | اصالت | استدلال استقرایی | حساسیت به مسئله | روانی ایده‌ها | بیان شفاهی | درک شفاهی | تشخیص گفتار | تشخیص رنگ بصری | کنترل نرخ</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>هنرمندان صنایع دستی | حکاکان و اسیدکاران | تنظیم‌کنندگان و اپراتورهای ماشین‌های فورجینگ و آهنگری فلز و پلاستیک | قالب‌سازان و ماهیچه‌سازان ریخته‌گری چدن و فولاد | رنگ‌کاران و پرداخت‌کاران مبلمان | دمندگان، قالب‌گیران، خم‌کاران و پرداخت‌کاران شیشه | کارگران پرداخت‌کاری و سنگ‌زنی دستی | تنظیم‌کنندگان و اپراتورهای ماشین‌ابزارهای سنگ‌زنی، لپینگ و پولیش فلز و پلاستیک | طلاسازان و سازندگان مصنوعات قیمتی و فلزات گرانبها | مدل‌سازان چوبی | قالب‌ریزان و شکل‌دهندگان مواد غیرفلزی و غیرپلاستیکی | کارگران نقاشی صنعتی، پوشش‌دهی و تزیین | الگوسازان صنعتی فلز و پلاستیک | الگوسازان چوبی صنعتی | ریخته‌گران و پاتیل‌ریزان فلزات | تعمیرکاران نسوزها و جداره‌های کوره | دوزندگان دستی | سنگ‌تراشان و حکاکان سنگ در خطوط تولید | سازندگان و مونتاژکاران اسکلت فلزی | سنگ‌زن‌ها و تیزکاران ابزار صنعتی</t>
+          <t>هنرمندان صنایع دستی | حکاکان و اسیدکاران | تنظیم‌کنندگان و اپراتورهای ماشین‌های فورجینگ فلز و پلاستیک | قالب‌گیران و ماهیچه‌سازان ریخته‌گری | پرداخت‌کاران و رنگ‌کاران چوب و مبلمان | دمندگان، قالب‌گیران، خم‌کاران و پرداخت‌کاران شیشه | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | جواهرسازان و سازندگان مصنوعات فلزی و سنگ‌های قیمتی | مدل‌سازان چوب | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | کارگران رنگ‌کاری، پوشش‌دهی و تزیین قطعات | الگوسازان فلز و پلاستیک | الگوسازان چوب | ریخته‌گران و متصدیان بارریزی مذاب فلزات | تعمیرکاران و نسوزکاران مواد دیرگداز صنعتی | دوزندگان دستی | سنگ‌تراشان و حکاکان صنعتی سنگ | سازندگان و مونتاژکاران سازه‌های فلزی | سنگ‌زن‌ها، سوهان‌کاران و تیزکاران ابزار</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>نظارت | تفکر انتقادی | سخن گفتن | شنیدن فعال</t>
+          <t>نظارت | تفکر انتقادی | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | مکانیک | ریاضیات | خدمات مشتریان و خدمات فردی | زبان انگلیسی</t>
+          <t>تولید و فرآوری | مکانیک | ریاضیات | خدمات مشتری و شخصی | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>دید نزدیک | دقت در کنترل | حساسیت به مسئله | ثبات دست و بازو | چابکی انگشتان | چابکی دستی | توجه انتخابی | مرتب‌سازی اطلاعات | بیان شفاهی | درک شفاهی | زمان واکنش | کنترل نرخ | استدلال قیاسی</t>
+          <t>بینایی نزدیک | دقت کنترل | حساسیت به مسئله | ثبات دست و بازو | مهارت انگشتان | مهارت دستی | توجه انتخابی | ترتیب‌دهی اطلاعات | بیان شفاهی | درک شفاهی | زمان عکس‌العمل | کنترل نرخ | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان ماشین‌های اتصال چسبی | تنظیم‌کنندگان و اپراتورهای ماشین‌های برش و اسلایسر | تنظیم‌کنندگان و اپراتورهای ماشین‌های برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های اکستروژن و کشش فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه‌ای | تنظیم‌کنندگان و اپراتورهای ماشین‌های اکستروژن، شکل‌دهی، پرس و فشرده‌سازی | کارگران پرداخت‌کاری و سنگ‌زنی دستی | تنظیم‌کنندگان و اپراتورهای ماشین‌ابزارهای سنگ‌زنی، لپینگ و پولیش فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تغذیه‌کنندگان و متصدیان تخلیه دستگاه‌های صنعتی | تنظیم‌کنندگان و اپراتورهای ماشین‌های فرز و رنده‌تراش فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌ابزارهای چندمنظوره فلز و پلاستیک | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | کارگران صحافی و خدمات تکمیلی چاپ | تنظیم‌کنندگان و اپراتورهای ماشین‌های نورد فلز و پلاستیک | اپراتورهای چرخ خیاطی صنعتی | تنظیم‌کنندگان و اپراتورهای ماشین‌های برش منسوجات | تنظیم‌کنندگان و اپراتورهای ماشین‌های تابندگی، بافندگی و کشش نخ | سنگ‌زن‌ها و تیزکاران ابزار صنعتی | تنظیم‌کنندگان و اپراتورهای ماشین‌آلات چوب‌بری به‌جز اره</t>
+          <t>اپراتورها و متصدیان ماشین‌های چسب‌زنی و اتصال | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | تنظیم‌کنندگان و اپراتورهای ماشین‌های برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های اکستروژن و کشش فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه‌ای | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکستروژن، فرم‌دهی، پرس و تراکم مواد | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌ابزارهای چندگانه فلز و پلاستیک | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | کارگران صحافی و تکمیل چاپ | تنظیم‌کنندگان و اپراتورهای ماشین‌های نورد فلز و پلاستیک | چرخکاران صنعتی | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های برش منسوجات | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های بوبین‌پیچی، تابندگی و کشش الیاف | سنگ‌زن‌ها، سوهان‌کاران و تیزکاران ابزار | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>نظارت | تفکر انتقادی | شنیدن فعال</t>
+          <t>نظارت | تفکر انتقادی | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | مدیریت و امور اداری | مکانیک</t>
+          <t>تولید و فرآوری | مدیریت و اداره | مکانیک</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>چابکی دستی | ثبات دست و بازو | دقت در کنترل | هماهنگی اندام‌ها | قدرت بالاتنه | کنترل نرخ | چابکی انگشتان | دید نزدیک | انعطاف‌پذیری گسترده بدن | قدرت ایستا | زمان واکنش | توجه انتخابی | حساسیت به مسئله | درک شفاهی | استقامت بدنی | تشخیص گفتار | توجه شنیداری</t>
+          <t>مهارت دستی | ثبات دست و بازو | دقت کنترل | هماهنگی چند عضو | قدرت تنه | کنترل نرخ | مهارت انگشتان | بینایی نزدیک | انعطاف‌پذیری دامنه حرکت | قدرت ایستا | زمان عکس‌العمل | توجه انتخابی | حساسیت به مسئله | درک شفاهی | استقامت | تشخیص گفتار | توجه شنیداری</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>مونتاژکاران سازه، سطوح، اتصالات و سیستم‌های هواپیما | صافکاران و تعمیرکاران بدنه خودرو | تنظیم‌کنندگان و اپراتورهای ماشین‌های پوشش‌دهی، رنگ‌کاری و اسپری | مونتاژکاران موتور و ماشین‌آلات صنعتی | تنظیم‌کنندگان و اپراتورهای ماشین‌های اکستروژن و کشش فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه‌ای | سازندگان و لمینیت‌کاران قطعات فایبرگلاس | قالب‌سازان و ماهیچه‌سازان ریخته‌گری چدن و فولاد | کارگران پرداخت‌کاری و سنگ‌زنی دستی | مکانیک‌های ماشین‌آلات صنعتی | عایق‌کاران کف، سقف و دیوار ساختمانی | عایق‌کاران سیستم‌های مکانیکی و تاسیساتی | قالب‌ریزان و شکل‌دهندگان مواد غیرفلزی و غیرپلاستیکی | تنظیم‌کنندگان و اپراتورهای ماشین‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های آبکاری فلز و پلاستیک | تعمیرکاران واگن‌های قطار | اپراتورها و متصدیان ماشین‌آلات تولید کفش | سازندگان و مونتاژکاران اسکلت فلزی | تعمیرکاران و تعویض‌کاران تایر خودرو | تنظیم‌کنندگان و اپراتورهای ماشین‌های جوشکاری و لحیم‌کاری</t>
+          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | صافکار و نقاش خودرو | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های پوشش‌دهی، رنگ‌کاری و اسپری | مونتاژکاران موتور و سایر ماشین‌آلات | تنظیم‌کنندگان و اپراتورهای ماشین‌های اکستروژن و کشش فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه‌ای | لایه‌نشانان و سازندگان فایبرگلاس | قالب‌گیران و ماهیچه‌سازان ریخته‌گری | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | مکانیک‌های ماشین‌آلات صنعتی | عایق‌کاران کف، سقف و دیوار | عایق‌کاران تاسیسات مکانیکی | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | تنظیم‌کاران و اپراتورهای ماشین‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک | تنظیم‌کاران و اپراتورهای دستگاه‌های آبکاری فلز و پلاستیک | تعمیرکار واگن قطار | اپراتورها و متصدیان ماشین‌آلات کفش | سازندگان و مونتاژکاران سازه‌های فلزی | آپاراتی و پنچرگیر و تعویض‌کار لاستیک | تنظیم‌کاران و اپراتورهای دستگاه‌های جوشکاری و لحیم‌کاری</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | سخن گفتن | تفکر انتقادی | درک مطلب</t>
+          <t>نظارت | گوش دادن فعال | سخن گفتن | تفکر انتقادی | درک مطلب</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>دید نزدیک | دقت در کنترل | قدرت ایستا | قدرت بالاتنه | چابکی دستی | هماهنگی اندام‌ها | چابکی انگشتان | ثبات دست و بازو | مرتب‌سازی اطلاعات | حساسیت به مسئله | انعطاف‌پذیری گسترده بدن | استقامت بدنی | سرعت ادراک | بیان شفاهی | درک شفاهی</t>
+          <t>بینایی نزدیک | دقت کنترل | قدرت ایستا | قدرت تنه | مهارت دستی | هماهنگی چند عضو | مهارت انگشتان | ثبات دست و بازو | ترتیب‌دهی اطلاعات | حساسیت به مسئله | انعطاف‌پذیری دامنه حرکت | استقامت | سرعت ادراکی | بیان شفاهی | درک شفاهی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان ماشین‌های اتصال چسبی | تنظیم‌کنندگان و اپراتورهای ماشین‌های برش و اسلایسر | کارگران پرداخت‌کاری و سنگ‌زنی دستی | تنظیم‌کنندگان و اپراتورهای ماشین‌ابزارهای سنگ‌زنی، لپینگ و پولیش فلز و پلاستیک | کمک‌بنایان، کمک‌آجرچین‌ها، کمک‌سنگ‌کاران و نصابان کاشی | کمک‌نجاران | کمک‌برق‌کاران | کارگران کمکی استخراج معدن | کارگران کمکی نصب، تعمیر و نگهداری | کارگران کمکی نقاشی ساختمان، گچ‌کاری و سیمان‌کاری | کارگران کمکی لوله‌کشی، تاسیسات و خطوط لوله | کارگران دستی حمل‌ونقل کالا و جابه‌جایی بار | کارگران رختشویخانه و خشک‌شویی | تغذیه‌کنندگان و متصدیان تخلیه دستگاه‌های صنعتی | کارگران تعمیر و نگهداری ماشین‌آلات | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | بسته‌بندهای دستی | تنظیم‌کنندگان و اپراتورهای ماشین‌های تولید محصولات کاغذی | سنگ‌زن‌ها و تیزکاران ابزار صنعتی | تنظیم‌کنندگان و اپراتورهای ماشین‌آلات چوب‌بری به‌جز اره</t>
+          <t>اپراتورها و متصدیان ماشین‌های چسب‌زنی و اتصال | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | کمک‌بناها، کمک‌بلوک‌چین‌ها، کمک‌سنگ‌تراشان و کمک‌نصابان کاشی و مرمر | کمک‌نجاران | کمک‌برق‌کاران | کارگران کمکی استخراج معدن | کارگران کمکی نصب، نگهداری و تعمیرات | کمک‌نقاشان، کمک‌کاغذدیواری‌کاران، کمک‌گچ‌کاران و کمک‌سیمان‌کاران | کمک‌لوله‌گذاران، کمک‌لوله‌کش‌ها، کمک‌نصابان لوله و بخار | کارگران جابه‌جایی دستی بار، کالا و مصالح | کارگران خشکشویی و رختشویخانه | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | کارگران تعمیر و نگهداری ماشین‌آلات | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | کارگران بسته‌بندی دستی | تنظیم‌کنندگان و اپراتورهای ماشین‌های تولید محصولات کاغذی | سنگ‌زن‌ها، سوهان‌کاران و تیزکاران ابزار | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>چابکی دستی | چابکی انگشتان | ثبات دست و بازو | هماهنگی اندام‌ها | دقت در کنترل | قدرت ایستا | قدرت بالاتنه | استقامت بدنی | دید نزدیک | دید دور | ادراک عمق | هماهنگی کلی بدن | تعادل بدنی | انعطاف‌پذیری گسترده بدن | زمان واکنش | حساسیت به مسئله | درک شفاهی | توجه انتخابی</t>
+          <t>مهارت دستی | مهارت انگشتان | ثبات دست و بازو | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | قدرت تنه | استقامت | بینایی نزدیک | بینایی دور | درک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری دامنه حرکت | زمان عکس‌العمل | حساسیت به مسئله | درک شفاهی | توجه انتخابی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>کمک‌کارگران خطوط تولید | مونتاژکاران گروهی | سایر مونتاژکاران و سازندگان قطعات | بازرسان، آزمون‌گران، تفکیک‌کنندگان، نمونه‌برداران و توزین‌کنندگان خطوط تولید | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | بسته‌بندهای دستی | تغذیه‌کنندگان و متصدیان تخلیه دستگاه‌های صنعتی | برشکاران دستی قطعات | کارگران پرداخت‌کاری و سنگ‌زنی دستی | تنظیم‌کنندگان و اپراتورهای ماشین‌های اختلاط و ترکیب مواد | اپراتورها و متصدیان کوره‌ها، خشک‌کن‌ها و دیگ‌های صنعتی | اپراتورها و متصدیان تجهیزات شستشو و اسیدشویی فلزات | اپراتورها و متصدیان ماشین‌های اتصال چسبی | کارگران نقاشی صنعتی، پوشش‌دهی و تزیین | اپراتورهای ماشین‌ابزارهای CNC | تراشکاران و فرزکاران ماشین‌ابزار | مکانیک‌های ماشین‌آلات صنعتی | سرپرستان رده اول کارگران تولید و عملیات | رانندگان لیفتراک و تراکتورهای صنعتی | کارگران دستی حمل‌ونقل کالا و جابه‌جایی بار</t>
+          <t>کمک‌کارگران خطوط تولید | مونتاژکاران گروهی | سایر مونتاژکاران و سازندگان | بازرسان، آزمونگران، تفکیک‌کنندگان، نمونه‌برداران و توزین‌گران | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | کارگران بسته‌بندی دستی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | برشکاران و پیرایشگران دستی | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های مخلوط‌کن و ترکیب مواد | اپراتورها و متصدیان کوره‌ها، خشک‌کن‌ها و پاتیل‌های صنعتی | اپراتورها و متصدیان تجهیزات شست‌وشو، نظافت و چربی‌زدایی فلزات | اپراتورها و متصدیان ماشین‌های چسب‌زنی و اتصال | کارگران رنگ‌کاری، پوشش‌دهی و تزیین قطعات | اپراتورهای ماشین‌ابزارهای کنترل عددی رایانه‌ای CNC | تراشکاران، فرزکاران و ماشین‌کاران قطعات دقیق | مکانیک‌های ماشین‌آلات صنعتی | سرپرستان رده اول کارگران تولید و عملیات | رانندگان و اپراتورهای تراکتور و لیفتراک صنعتی | کارگران جابه‌جایی دستی بار، کالا و مصالح</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
